--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -478,16 +490,16 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9815607070922852</v>
+        <v>0.9812558889389038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9141876697540283</v>
+        <v>0.9178223609924316</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9593338370323181</v>
+        <v>0.9278562068939209</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4251857995986938</v>
+        <v>0.1246784031391144</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -516,16 +528,16 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9284228682518005</v>
+        <v>0.9254208207130432</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07992354780435562</v>
+        <v>0.07704853266477585</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,10 +545,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9185376763343811</v>
+        <v>0.9178934097290039</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0542241707444191</v>
+        <v>0.07876484096050262</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,16 +566,16 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9714100360870361</v>
+        <v>0.9717703461647034</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6809857487678528</v>
+        <v>0.7107669115066528</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,10 +583,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9510252475738525</v>
+        <v>0.9289593696594238</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2851166725158691</v>
+        <v>0.1311951726675034</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -592,16 +604,16 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9563748240470886</v>
+        <v>0.9625841975212097</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3470132946968079</v>
+        <v>0.4925026595592499</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,14 +621,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9412764310836792</v>
+        <v>0.8718294501304626</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1741597652435303</v>
+        <v>0.01034031342715025</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -630,16 +642,16 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9457223415374756</v>
+        <v>0.9448919892311096</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2004490047693253</v>
+        <v>0.209463357925415</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,10 +659,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9261298179626465</v>
+        <v>0.9165523648262024</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0799017995595932</v>
+        <v>0.07406295835971832</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -668,16 +680,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9629274606704712</v>
+        <v>0.9741333723068237</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4758066534996033</v>
+        <v>0.7684860825538635</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +697,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9534151554107666</v>
+        <v>0.9450781345367432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3207159042358398</v>
+        <v>0.2740852236747742</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -706,16 +718,16 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9687432646751404</v>
+        <v>0.9757571816444397</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6133853793144226</v>
+        <v>0.8067728281021118</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,10 +735,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.974687397480011</v>
+        <v>0.9750929474830627</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7817203402519226</v>
+        <v>0.84089595079422</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -744,16 +756,16 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8694075345993042</v>
+        <v>0.8675680160522461</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004209341015666723</v>
+        <v>0.004715813789516687</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,10 +773,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9503775238990784</v>
+        <v>0.9570215940475464</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2760900855064392</v>
+        <v>0.4582810699939728</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -782,16 +794,16 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9554357528686523</v>
+        <v>0.952984631061554</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3310798704624176</v>
+        <v>0.3140316605567932</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -799,10 +811,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.9678035378456116</v>
+        <v>0.9468457102775574</v>
       </c>
       <c r="I10" t="n">
-        <v>0.613148033618927</v>
+        <v>0.2965426743030548</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -820,16 +832,16 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>0.96612548828125</v>
+        <v>0.9452314376831055</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5492395758628845</v>
+        <v>0.2131072282791138</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -837,10 +849,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8896226286888123</v>
+        <v>0.8811273574829102</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01305496226996183</v>
+        <v>0.01532776188105345</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -858,16 +870,16 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9403905868530273</v>
+        <v>0.9320643544197083</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1511375308036804</v>
+        <v>0.1084205284714699</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -875,10 +887,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.984317421913147</v>
+        <v>0.9848693609237671</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9602999687194824</v>
+        <v>0.977561354637146</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -896,16 +908,16 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8883476257324219</v>
+        <v>0.8733993768692017</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01032054517418146</v>
+        <v>0.006136762909591198</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,14 +925,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.888104259967804</v>
+        <v>0.9658039212226868</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01214755699038506</v>
+        <v>0.6395894289016724</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -934,16 +946,16 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9466218948364258</v>
+        <v>0.9512802362442017</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2101627439260483</v>
+        <v>0.2887421548366547</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -951,10 +963,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8472374081611633</v>
+        <v>0.8613146543502808</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001943458220921457</v>
+        <v>0.006696123164147139</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,16 +984,16 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>0.876516580581665</v>
+        <v>0.8642752170562744</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005861489102244377</v>
+        <v>0.004071579314768314</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -989,10 +1001,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9740236401557922</v>
+        <v>0.9740416407585144</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7658466696739197</v>
+        <v>0.8197910785675049</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1010,16 +1022,16 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9654644131660461</v>
+        <v>0.9777562022209167</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5335628390312195</v>
+        <v>0.8511855602264404</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1027,10 +1039,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9317580461502075</v>
+        <v>0.9388236999511719</v>
       </c>
       <c r="I16" t="n">
-        <v>0.106723465025425</v>
+        <v>0.2065253406763077</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1048,16 +1060,16 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9522076845169067</v>
+        <v>0.9548295736312866</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2809933423995972</v>
+        <v>0.3435360193252563</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1065,10 +1077,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.9797279834747314</v>
+        <v>0.972326934337616</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8908001184463501</v>
+        <v>0.7838471531867981</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1086,16 +1098,16 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>0.877234935760498</v>
+        <v>0.8688458800315857</v>
       </c>
       <c r="F18" t="n">
-        <v>0.006063130218535662</v>
+        <v>0.004994218703359365</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1103,10 +1115,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.95649653673172</v>
+        <v>0.9524815082550049</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3721508681774139</v>
+        <v>0.3791241943836212</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1124,16 +1136,16 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9538020491600037</v>
+        <v>0.9542009830474854</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3048391342163086</v>
+        <v>0.3332308530807495</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1141,14 +1153,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.9227530956268311</v>
+        <v>0.8797593116760254</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06721364706754684</v>
+        <v>0.01445733103901148</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -1162,16 +1174,16 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9390206933021545</v>
+        <v>0.943764328956604</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1405135840177536</v>
+        <v>0.1977777630090714</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1179,10 +1191,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.9521746635437012</v>
+        <v>0.9406015276908875</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3017818033695221</v>
+        <v>0.2239515334367752</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1200,16 +1212,16 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9635236263275146</v>
+        <v>0.9625943303108215</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4890150129795074</v>
+        <v>0.4927229285240173</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1217,14 +1229,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8574357628822327</v>
+        <v>0.922931969165802</v>
       </c>
       <c r="I21" t="n">
-        <v>0.003013405948877335</v>
+        <v>0.09932664036750793</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1238,16 +1250,16 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8901019692420959</v>
+        <v>0.8936896324157715</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01124140340834856</v>
+        <v>0.01585591211915016</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1255,10 +1267,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8839223384857178</v>
+        <v>0.8801813721656799</v>
       </c>
       <c r="I22" t="n">
-        <v>0.009976165369153023</v>
+        <v>0.01472015678882599</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1276,16 +1288,16 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9813882112503052</v>
+        <v>0.9802749156951904</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9111661911010742</v>
+        <v>0.9008755683898926</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1293,14 +1305,14 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.8204303383827209</v>
+        <v>0.9462042450904846</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0006480262381955981</v>
+        <v>0.2882097661495209</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1314,16 +1326,16 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9610583186149597</v>
+        <v>0.9574074745178223</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4359547793865204</v>
+        <v>0.3885829150676727</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.9720549583435059</v>
+        <v>0.964493989944458</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7177890539169312</v>
+        <v>0.610785186290741</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1352,16 +1364,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9582468271255493</v>
+        <v>0.9561952948570251</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3806631565093994</v>
+        <v>0.3668406903743744</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.9764389991760254</v>
+        <v>0.9427069425582886</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8223161101341248</v>
+        <v>0.2463701963424683</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1390,16 +1402,16 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7606517672538757</v>
+        <v>0.7499914765357971</v>
       </c>
       <c r="F26" t="n">
-        <v>5.369010614231229e-05</v>
+        <v>4.979018922313116e-05</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1407,14 +1419,14 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.908534824848175</v>
+        <v>0.9285922050476074</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03278478607535362</v>
+        <v>0.1289893388748169</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1428,16 +1440,16 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9379069209098816</v>
+        <v>0.9424656629562378</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1324219852685928</v>
+        <v>0.1850894838571548</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1445,14 +1457,14 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.9319831728935242</v>
+        <v>0.8927420377731323</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1079679727554321</v>
+        <v>0.02537095919251442</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -1466,16 +1478,16 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9802772998809814</v>
+        <v>0.9824098348617554</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8905489444732666</v>
+        <v>0.9357606172561646</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.9359010457992554</v>
+        <v>0.9092923402786255</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1321168839931488</v>
+        <v>0.05317321419715881</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1504,27 +1516,27 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9254499673843384</v>
+        <v>0.9161902666091919</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06827320158481598</v>
+        <v>0.04814314469695091</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9621320962905884</v>
+        <v>0.9512698650360107</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4827378392219543</v>
+        <v>0.3599153161048889</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1542,16 +1554,16 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8897067904472351</v>
+        <v>0.8920061588287354</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0110266599804163</v>
+        <v>0.01462652813643217</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1559,14 +1571,14 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.9072896242141724</v>
+        <v>0.9241102933883667</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03081658482551575</v>
+        <v>0.1048757806420326</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1580,16 +1592,16 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9410327672958374</v>
+        <v>0.9400609731674194</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1563854515552521</v>
+        <v>0.1636356711387634</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1597,10 +1609,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.9543173313140869</v>
+        <v>0.9349057078361511</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3351181745529175</v>
+        <v>0.1725754141807556</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1618,16 +1630,16 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8960103988647461</v>
+        <v>0.8931522369384766</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01503598876297474</v>
+        <v>0.01545204687863588</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.9257655739784241</v>
+        <v>0.9529797434806824</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07842286676168442</v>
+        <v>0.3872579634189606</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1656,16 +1668,16 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9294837713241577</v>
+        <v>0.9334372282028198</v>
       </c>
       <c r="F33" t="n">
-        <v>0.08455650508403778</v>
+        <v>0.1163673177361488</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1673,10 +1685,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.9201833009719849</v>
+        <v>0.9327374696731567</v>
       </c>
       <c r="I33" t="n">
-        <v>0.05895629152655602</v>
+        <v>0.1561808288097382</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1694,16 +1706,16 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9528168439865112</v>
+        <v>0.9611902236938477</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2899025976657867</v>
+        <v>0.4628022611141205</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.9594314098358154</v>
+        <v>0.9373622536659241</v>
       </c>
       <c r="I34" t="n">
-        <v>0.427105575799942</v>
+        <v>0.1931723654270172</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1732,16 +1744,16 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9651399850845337</v>
+        <v>0.966513454914093</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5259584784507751</v>
+        <v>0.5821634531021118</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1749,10 +1761,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.974880039691925</v>
+        <v>0.9456994533538818</v>
       </c>
       <c r="I35" t="n">
-        <v>0.786284327507019</v>
+        <v>0.2818000912666321</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1770,16 +1782,16 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D36" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9675746560096741</v>
+        <v>0.9689645767211914</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5843831300735474</v>
+        <v>0.6414813995361328</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1787,10 +1799,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.9630584120750427</v>
+        <v>0.9637142419815063</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5028780102729797</v>
+        <v>0.593845546245575</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1808,16 +1820,16 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9764668941497803</v>
+        <v>0.9665493965148926</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8074016571044922</v>
+        <v>0.5830174088478088</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1825,14 +1837,14 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.9422587156295776</v>
+        <v>0.9048599600791931</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1831414848566055</v>
+        <v>0.04351432248950005</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -1846,16 +1858,16 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E38" t="n">
-        <v>0.961496114730835</v>
+        <v>0.964801549911499</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4450725317001343</v>
+        <v>0.5421174764633179</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1863,10 +1875,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.958850622177124</v>
+        <v>0.9534032344818115</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4157685935497284</v>
+        <v>0.3942798376083374</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1884,16 +1896,16 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9817562103271484</v>
+        <v>0.9838773012161255</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9175519943237305</v>
+        <v>0.9552214741706848</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1901,10 +1913,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.952088475227356</v>
+        <v>0.9127433300018311</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3005031645298004</v>
+        <v>0.06221776083111763</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1922,16 +1934,16 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9502402544021606</v>
+        <v>0.9268733859062195</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2538694143295288</v>
+        <v>0.08301041275262833</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1939,10 +1951,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.9545594453811646</v>
+        <v>0.9617869257926941</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3390752077102661</v>
+        <v>0.5528327822685242</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1960,16 +1972,16 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9375214576721191</v>
+        <v>0.9369739890098572</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1297307759523392</v>
+        <v>0.1396215260028839</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1977,10 +1989,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.926119327545166</v>
+        <v>0.9188265204429626</v>
       </c>
       <c r="I41" t="n">
-        <v>0.07985885441303253</v>
+        <v>0.08221547305583954</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1998,16 +2010,16 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E42" t="n">
-        <v>0.946138322353363</v>
+        <v>0.9431710243225098</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2048866748809814</v>
+        <v>0.1918810456991196</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2015,10 +2027,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.8604543209075928</v>
+        <v>0.9021517038345337</v>
       </c>
       <c r="I42" t="n">
-        <v>0.003439108375459909</v>
+        <v>0.03852802887558937</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2036,16 +2048,16 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D43" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9383211731910706</v>
+        <v>0.9439684748649597</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1353762596845627</v>
+        <v>0.1998456567525864</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2053,10 +2065,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.9714243412017822</v>
+        <v>0.9574533700942993</v>
       </c>
       <c r="I43" t="n">
-        <v>0.702216625213623</v>
+        <v>0.4663883149623871</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2074,16 +2086,16 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E44" t="n">
-        <v>0.970970094203949</v>
+        <v>0.9665215015411377</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6697565317153931</v>
+        <v>0.582353413105011</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2091,10 +2103,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.966519296169281</v>
+        <v>0.9241686463356018</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5823016166687012</v>
+        <v>0.1051585450768471</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2112,16 +2124,16 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9196617603302002</v>
+        <v>0.9260676503181458</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05033284053206444</v>
+        <v>0.07964737713336945</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2129,10 +2141,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.9724276065826416</v>
+        <v>0.9761473536491394</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7269652485847473</v>
+        <v>0.8611717820167542</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2150,16 +2162,16 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D46" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9224532246589661</v>
+        <v>0.921064019203186</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05828430131077766</v>
+        <v>0.0616617277264595</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2167,10 +2179,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.9420469999313354</v>
+        <v>0.9329687356948853</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1811681538820267</v>
+        <v>0.1578539907932281</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2188,16 +2200,16 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9284443855285645</v>
+        <v>0.9175384044647217</v>
       </c>
       <c r="F47" t="n">
-        <v>0.08001510798931122</v>
+        <v>0.05154374614357948</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2205,10 +2217,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9542589783668518</v>
+        <v>0.9566681981086731</v>
       </c>
       <c r="I47" t="n">
-        <v>0.334170013666153</v>
+        <v>0.4517187774181366</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2226,16 +2238,16 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9478974938392639</v>
+        <v>0.9388810992240906</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2247017025947571</v>
+        <v>0.1540132910013199</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2243,10 +2255,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9624738693237305</v>
+        <v>0.9783727526664734</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4901090562343597</v>
+        <v>0.9003597497940063</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2264,31 +2276,31 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9109808802604675</v>
+        <v>0.9189687371253967</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03205707669258118</v>
+        <v>0.05542448535561562</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.921169102191925</v>
+        <v>0.8820403814315796</v>
       </c>
       <c r="I49" t="n">
-        <v>0.06199299544095993</v>
+        <v>0.01593939401209354</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -2302,16 +2314,16 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9709534049034119</v>
+        <v>0.9669568538665771</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6693298816680908</v>
+        <v>0.5927428007125854</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2319,14 +2331,14 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.7506080865859985</v>
+        <v>0.9268447756767273</v>
       </c>
       <c r="I50" t="n">
-        <v>5.083386713522486e-05</v>
+        <v>0.1189883574843407</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -2340,16 +2352,16 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D51" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9799668192863464</v>
+        <v>0.9810988903045654</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8844491243362427</v>
+        <v>0.9152114391326904</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2357,10 +2369,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.9605671763420105</v>
+        <v>0.9556949734687805</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4499260187149048</v>
+        <v>0.4339909255504608</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2378,27 +2390,27 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D52" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9175279140472412</v>
+        <v>0.9295893907546997</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04501670226454735</v>
+        <v>0.0954480841755867</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9042229652404785</v>
+        <v>0.9067223072052002</v>
       </c>
       <c r="I52" t="n">
-        <v>0.02647799625992775</v>
+        <v>0.04732938855886459</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2416,16 +2428,16 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8925153017044067</v>
+        <v>0.8969894647598267</v>
       </c>
       <c r="F53" t="n">
-        <v>0.01265235897153616</v>
+        <v>0.01859223656356335</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2433,14 +2445,14 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8197695016860962</v>
+        <v>0.932496190071106</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0006313107442110777</v>
+        <v>0.1544536054134369</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -2454,16 +2466,16 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9510402679443359</v>
+        <v>0.9548076987266541</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2646002769470215</v>
+        <v>0.3431730568408966</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2471,10 +2483,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.9631021022796631</v>
+        <v>0.9304236769676208</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5038408637046814</v>
+        <v>0.1403709053993225</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2492,16 +2504,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D55" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9286004304885864</v>
+        <v>0.9335173964500427</v>
       </c>
       <c r="F55" t="n">
-        <v>0.08068063855171204</v>
+        <v>0.1168487444519997</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9216585755348206</v>
+        <v>0.935994029045105</v>
       </c>
       <c r="I55" t="n">
-        <v>0.06356016546487808</v>
+        <v>0.181424543261528</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2530,16 +2542,16 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D56" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8978190422058105</v>
+        <v>0.8997306823730469</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01645113527774811</v>
+        <v>0.02124243043363094</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2547,10 +2559,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9496405720710754</v>
+        <v>0.9706549048423767</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2661312222480774</v>
+        <v>0.7475012540817261</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2568,16 +2580,16 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9283934235572815</v>
+        <v>0.9314499497413635</v>
       </c>
       <c r="F57" t="n">
-        <v>0.07979873567819595</v>
+        <v>0.1050432100892067</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.9316039681434631</v>
+        <v>0.9264540672302246</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1058795973658562</v>
+        <v>0.1168606579303741</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2606,16 +2618,16 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E58" t="n">
-        <v>0.964672863483429</v>
+        <v>0.9609825015068054</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5151182413101196</v>
+        <v>0.4584819674491882</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2623,10 +2635,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.7835795283317566</v>
+        <v>0.8972709178924561</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0001606784644536674</v>
+        <v>0.03099005296826363</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2644,16 +2656,16 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D59" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9309113025665283</v>
+        <v>0.9232693910598755</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0912247821688652</v>
+        <v>0.06901133060455322</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2661,10 +2673,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.9900543093681335</v>
+        <v>0.9517224431037903</v>
       </c>
       <c r="I59" t="n">
-        <v>0.996349036693573</v>
+        <v>0.3669953048229218</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2682,16 +2694,16 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D60" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9434352517127991</v>
+        <v>0.9509047269821167</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1776413172483444</v>
+        <v>0.2834172248840332</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2699,10 +2711,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.9808189868927002</v>
+        <v>0.9872685670852661</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9104594588279724</v>
+        <v>0.9907346963882446</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2720,16 +2732,16 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D61" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9633265733718872</v>
+        <v>0.9674261808395386</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4846229255199432</v>
+        <v>0.6040238738059998</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2737,10 +2749,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.9706239700317383</v>
+        <v>0.9533031582832336</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6824154853820801</v>
+        <v>0.3926116824150085</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2758,16 +2770,16 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8959100842475891</v>
+        <v>0.8849295973777771</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01496133301407099</v>
+        <v>0.01045867335051298</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2775,10 +2787,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.9512630701065063</v>
+        <v>0.941638708114624</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2884964346885681</v>
+        <v>0.2347470819950104</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2796,16 +2808,16 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D63" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9672372937202454</v>
+        <v>0.9746760725975037</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5761131048202515</v>
+        <v>0.7814508676528931</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2813,14 +2825,14 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.6246751546859741</v>
+        <v>0.9287039637565613</v>
       </c>
       <c r="I63" t="n">
-        <v>1.179000491902116e-06</v>
+        <v>0.1296566277742386</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -2834,16 +2846,16 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9511042237281799</v>
+        <v>0.9444299936294556</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2654748857021332</v>
+        <v>0.2045983970165253</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2851,10 +2863,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.8115222454071045</v>
+        <v>0.8151840567588806</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0004572769103106111</v>
+        <v>0.00113022152800113</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2872,31 +2884,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D65" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9121094942092896</v>
+        <v>0.9384326934814453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.03397778794169426</v>
+        <v>0.1505036354064941</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.7465673685073853</v>
+        <v>0.9451685547828674</v>
       </c>
       <c r="I65" t="n">
-        <v>4.439441909198649e-05</v>
+        <v>0.2751960158348083</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -2910,16 +2922,16 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9541690945625305</v>
+        <v>0.9593924880027771</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3105729818344116</v>
+        <v>0.4263385534286499</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2927,10 +2939,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.9542753100395203</v>
+        <v>0.9196028709411621</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3344356417655945</v>
+        <v>0.08520399034023285</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2948,16 +2960,16 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E67" t="n">
-        <v>0.968600869178772</v>
+        <v>0.9398431181907654</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6098237037658691</v>
+        <v>0.1618157625198364</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2965,10 +2977,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.8954246640205383</v>
+        <v>0.8952063322067261</v>
       </c>
       <c r="I67" t="n">
-        <v>0.01723741926252842</v>
+        <v>0.02828199230134487</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2986,16 +2998,16 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9455940723419189</v>
+        <v>0.9411020278930664</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1990987956523895</v>
+        <v>0.1726104468107224</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3003,10 +3015,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.9277535676956177</v>
+        <v>0.9422557950019836</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08684969693422318</v>
+        <v>0.2413982897996902</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3024,16 +3036,16 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D69" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8458822965621948</v>
+        <v>0.8457671403884888</v>
       </c>
       <c r="F69" t="n">
-        <v>0.001472608069889247</v>
+        <v>0.001826161285862327</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8857508897781372</v>
+        <v>0.8664589524269104</v>
       </c>
       <c r="I69" t="n">
-        <v>0.01087033841758966</v>
+        <v>0.008270629681646824</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3062,16 +3074,16 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D70" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9767310619354248</v>
+        <v>0.9681288599967957</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8136529326438904</v>
+        <v>0.6210507154464722</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3079,10 +3091,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.9288931488990784</v>
+        <v>0.9644365906715393</v>
       </c>
       <c r="I70" t="n">
-        <v>0.09209001064300537</v>
+        <v>0.6095322370529175</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3100,16 +3112,16 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D71" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9696776866912842</v>
+        <v>0.9676597714424133</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6369044184684753</v>
+        <v>0.6096665859222412</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3117,10 +3129,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.9104451537132263</v>
+        <v>0.9012036323547363</v>
       </c>
       <c r="I71" t="n">
-        <v>0.03606323525309563</v>
+        <v>0.03692644834518433</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3138,16 +3150,16 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D72" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9305321574211121</v>
+        <v>0.9265028834342957</v>
       </c>
       <c r="F72" t="n">
-        <v>0.08940330892801285</v>
+        <v>0.08144643157720566</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.9503687620162964</v>
+        <v>0.9691630005836487</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2759693264961243</v>
+        <v>0.7144370079040527</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3176,16 +3188,16 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D73" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9355283975601196</v>
+        <v>0.9322745203971863</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1166584342718124</v>
+        <v>0.1096008867025375</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3193,10 +3205,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.9576336145401001</v>
+        <v>0.9681295156478882</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3927494585514069</v>
+        <v>0.6913739442825317</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3214,16 +3226,16 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D74" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9600203633308411</v>
+        <v>0.9645033478736877</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4148803055286407</v>
+        <v>0.5352874398231506</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3231,10 +3243,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9311262965202332</v>
+        <v>0.9706757664680481</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1033065840601921</v>
+        <v>0.7479603290557861</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3252,16 +3264,16 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9659350514411926</v>
+        <v>0.9737765192985535</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5446981191635132</v>
+        <v>0.759884774684906</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3269,14 +3281,14 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.9102035760879517</v>
+        <v>0.9316759705543518</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03563045710325241</v>
+        <v>0.1487210243940353</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3290,16 +3302,16 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D76" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9778051376342773</v>
+        <v>0.9820473790168762</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8384357094764709</v>
+        <v>0.9303677082061768</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3307,10 +3319,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9721739888191223</v>
+        <v>0.9598134756088257</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7207231521606445</v>
+        <v>0.5123750567436218</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3328,16 +3340,16 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9708918333053589</v>
+        <v>0.967781662940979</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6677595376968384</v>
+        <v>0.6126189231872559</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3345,10 +3357,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9205379486083984</v>
+        <v>0.9267030358314514</v>
       </c>
       <c r="I77" t="n">
-        <v>0.06003068387508392</v>
+        <v>0.1182119771838188</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3366,27 +3378,27 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D78" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9166169762611389</v>
+        <v>0.9399588108062744</v>
       </c>
       <c r="F78" t="n">
-        <v>0.04292769730091095</v>
+        <v>0.1627798080444336</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.9581232666969299</v>
+        <v>0.9704426527023315</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4018906056880951</v>
+        <v>0.7428249716758728</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3404,16 +3416,16 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D79" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9616842269897461</v>
+        <v>0.9674438834190369</v>
       </c>
       <c r="F79" t="n">
-        <v>0.449030876159668</v>
+        <v>0.6044507026672363</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3421,10 +3433,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.8520661592483521</v>
+        <v>0.824892520904541</v>
       </c>
       <c r="I79" t="n">
-        <v>0.002388459397479892</v>
+        <v>0.001616854104213417</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3442,16 +3454,16 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D80" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E80" t="n">
-        <v>0.907443642616272</v>
+        <v>0.9092383980751038</v>
       </c>
       <c r="F80" t="n">
-        <v>0.02673895470798016</v>
+        <v>0.03395450115203857</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3459,10 +3471,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.9629954695701599</v>
+        <v>0.9385671615600586</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5014930963516235</v>
+        <v>0.2041193842887878</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3480,16 +3492,16 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D81" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9322644472122192</v>
+        <v>0.9303853511810303</v>
       </c>
       <c r="F81" t="n">
-        <v>0.098037488758564</v>
+        <v>0.09943979233503342</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3497,10 +3509,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.8879902362823486</v>
+        <v>0.9070650339126587</v>
       </c>
       <c r="I81" t="n">
-        <v>0.01208217348903418</v>
+        <v>0.04806846752762794</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3518,16 +3530,16 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D82" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9566259384155273</v>
+        <v>0.9596893191337585</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3513807058334351</v>
+        <v>0.4322124719619751</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3535,10 +3547,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.7718542218208313</v>
+        <v>0.7557240724563599</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0001056847613654099</v>
+        <v>0.0001486674591433257</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3556,16 +3568,16 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D83" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8824001550674438</v>
+        <v>0.8747684955596924</v>
       </c>
       <c r="F83" t="n">
-        <v>0.007747952360659838</v>
+        <v>0.00653217826038599</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3573,10 +3585,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.93785160779953</v>
+        <v>0.9257531762123108</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1460721492767334</v>
+        <v>0.1131388694047928</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3594,16 +3606,16 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E84" t="n">
-        <v>0.901020348072052</v>
+        <v>0.9024438858032227</v>
       </c>
       <c r="F84" t="n">
-        <v>0.01931044831871986</v>
+        <v>0.02425885014235973</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3611,10 +3623,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.9579986929893494</v>
+        <v>0.9113525748252869</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3995501399040222</v>
+        <v>0.05839532241225243</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3632,16 +3644,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9529025554656982</v>
+        <v>0.9482172727584839</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2911754548549652</v>
+        <v>0.2478149086236954</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,10 +3661,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.8620085716247559</v>
+        <v>0.8748853206634521</v>
       </c>
       <c r="I85" t="n">
-        <v>0.003682796144858003</v>
+        <v>0.01175693608820438</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3670,31 +3682,31 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8980621099472046</v>
+        <v>0.9431886672973633</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01665172539651394</v>
+        <v>0.1920541524887085</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.9163829684257507</v>
+        <v>0.9195557832717896</v>
       </c>
       <c r="I86" t="n">
-        <v>0.04861463233828545</v>
+        <v>0.08501975238323212</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3708,16 +3720,16 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D87" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8975961804389954</v>
+        <v>0.8810587525367737</v>
       </c>
       <c r="F87" t="n">
-        <v>0.01626945286989212</v>
+        <v>0.008728604763746262</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3725,14 +3737,14 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.9080418944358826</v>
+        <v>0.9600874781608582</v>
       </c>
       <c r="I87" t="n">
-        <v>0.03199036419391632</v>
+        <v>0.5178890228271484</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3746,16 +3758,16 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D88" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E88" t="n">
-        <v>0.969534695148468</v>
+        <v>0.9642680883407593</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6332899332046509</v>
+        <v>0.529932975769043</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3763,14 +3775,14 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.9211538434028625</v>
+        <v>0.8875146508216858</v>
       </c>
       <c r="I88" t="n">
-        <v>0.06194477528333664</v>
+        <v>0.02018908224999905</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3784,16 +3796,16 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D89" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9528120160102844</v>
+        <v>0.9475992321968079</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2898308336734772</v>
+        <v>0.2402266561985016</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3801,10 +3813,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.8332679271697998</v>
+        <v>0.8516899347305298</v>
       </c>
       <c r="I89" t="n">
-        <v>0.001086123054847121</v>
+        <v>0.004542833659797907</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3822,16 +3834,16 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D90" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9450313448905945</v>
+        <v>0.9473417997360229</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1932778060436249</v>
+        <v>0.2371292263269424</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3839,10 +3851,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.8694861531257629</v>
+        <v>0.8647078275680542</v>
       </c>
       <c r="I90" t="n">
-        <v>0.005140226799994707</v>
+        <v>0.00769463274627924</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3860,27 +3872,27 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9141699075698853</v>
+        <v>0.9195628762245178</v>
       </c>
       <c r="F91" t="n">
-        <v>0.03779996559023857</v>
+        <v>0.05712411552667618</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.9633210897445679</v>
+        <v>0.9687789082527161</v>
       </c>
       <c r="I91" t="n">
-        <v>0.5086824297904968</v>
+        <v>0.7058736681938171</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3898,16 +3910,16 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D92" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9466615319252014</v>
+        <v>0.9451123476028442</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2106011807918549</v>
+        <v>0.2118218541145325</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3915,10 +3927,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.9216833710670471</v>
+        <v>0.9263502955436707</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06364072114229202</v>
+        <v>0.1163019686937332</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3936,16 +3948,16 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E93" t="n">
-        <v>0.94058758020401</v>
+        <v>0.9361519813537598</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1527291387319565</v>
+        <v>0.1338351964950562</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3953,10 +3965,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.9342039823532104</v>
+        <v>0.9350883960723877</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1210564896464348</v>
+        <v>0.174031138420105</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3974,16 +3986,16 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D94" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E94" t="n">
-        <v>0.934807300567627</v>
+        <v>0.9364147186279297</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1122600808739662</v>
+        <v>0.1356587111949921</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3991,10 +4003,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.9667590260505676</v>
+        <v>0.9394024610519409</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5880133509635925</v>
+        <v>0.2120521813631058</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4012,16 +4024,16 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D95" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E95" t="n">
-        <v>0.95228511095047</v>
+        <v>0.9590838551521301</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2821119725704193</v>
+        <v>0.4202938973903656</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4029,10 +4041,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.9381172060966492</v>
+        <v>0.9652295708656311</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1480815261602402</v>
+        <v>0.6269128322601318</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4050,27 +4062,27 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D96" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9149155616760254</v>
+        <v>0.923066258430481</v>
       </c>
       <c r="F96" t="n">
-        <v>0.03929128870368004</v>
+        <v>0.06829819828271866</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.9170268774032593</v>
+        <v>0.9151478409767151</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0502251535654068</v>
+        <v>0.06944645196199417</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4088,16 +4100,16 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D97" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9517413973808289</v>
+        <v>0.9617530703544617</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2743392884731293</v>
+        <v>0.4746489822864532</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4105,10 +4117,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.8977258205413818</v>
+        <v>0.9035669565200806</v>
       </c>
       <c r="I97" t="n">
-        <v>0.01926805451512337</v>
+        <v>0.04105479642748833</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4126,16 +4138,16 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9298709034919739</v>
+        <v>0.9351296424865723</v>
       </c>
       <c r="F98" t="n">
-        <v>0.08631435036659241</v>
+        <v>0.1269700080156326</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4143,14 +4155,14 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.9345412850379944</v>
+        <v>0.9053236842155457</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1231788471341133</v>
+        <v>0.04443328827619553</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4164,16 +4176,16 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D99" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8774620294570923</v>
+        <v>0.8837973475456238</v>
       </c>
       <c r="F99" t="n">
-        <v>0.006128405686467886</v>
+        <v>0.009917950257658958</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4181,10 +4193,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.933379054069519</v>
+        <v>0.951445460319519</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1160189583897591</v>
+        <v>0.3626487851142883</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4202,16 +4214,16 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D100" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9356104135513306</v>
+        <v>0.9387742877006531</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1171694546937943</v>
+        <v>0.1531702429056168</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4219,10 +4231,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.9815222024917603</v>
+        <v>0.9557785987854004</v>
       </c>
       <c r="I100" t="n">
-        <v>0.92215895652771</v>
+        <v>0.4354938566684723</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4240,16 +4252,16 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D101" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9736426472663879</v>
+        <v>0.9430766701698303</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7378309369087219</v>
+        <v>0.190958559513092</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4257,10 +4269,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.8876262903213501</v>
+        <v>0.8918215036392212</v>
       </c>
       <c r="I101" t="n">
-        <v>0.01187588926404715</v>
+        <v>0.02436580695211887</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4278,16 +4290,16 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D102" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9587312936782837</v>
+        <v>0.9524270296096802</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3897847533226013</v>
+        <v>0.3055531084537506</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4295,10 +4307,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.9174873232841492</v>
+        <v>0.9698482155799866</v>
       </c>
       <c r="I102" t="n">
-        <v>0.05141054093837738</v>
+        <v>0.7296723127365112</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4316,16 +4328,16 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D103" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9413222074508667</v>
+        <v>0.9463495016098022</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1588092297315598</v>
+        <v>0.2255353182554245</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4333,14 +4345,14 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.821589469909668</v>
+        <v>0.9645014405250549</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0006784900324419141</v>
+        <v>0.6109474897384644</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4354,16 +4366,16 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D104" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9893471598625183</v>
+        <v>0.9850272536277771</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9935876131057739</v>
+        <v>0.9677433967590332</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4371,10 +4383,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.8372641205787659</v>
+        <v>0.8525604009628296</v>
       </c>
       <c r="I104" t="n">
-        <v>0.001280043972656131</v>
+        <v>0.004703289363533258</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4392,16 +4404,16 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8602278828620911</v>
+        <v>0.8616166114807129</v>
       </c>
       <c r="F105" t="n">
-        <v>0.002771398052573204</v>
+        <v>0.003619659459218383</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4409,10 +4421,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9678220152854919</v>
+        <v>0.9620802402496338</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6135969758033752</v>
+        <v>0.5589864253997803</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4430,16 +4442,16 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D106" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9599656462669373</v>
+        <v>0.9701977968215942</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4137911796569824</v>
+        <v>0.6718748807907104</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4447,14 +4459,14 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.8082947134971619</v>
+        <v>0.9583548307418823</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0004037759790662676</v>
+        <v>0.4836257994174957</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4468,16 +4480,16 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D107" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9288274645805359</v>
+        <v>0.9343733787536621</v>
       </c>
       <c r="F107" t="n">
-        <v>0.08165911585092545</v>
+        <v>0.1221177726984024</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4485,10 +4497,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.9773390293121338</v>
+        <v>0.9795598387718201</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8422254323959351</v>
+        <v>0.9189029932022095</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4506,16 +4518,16 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D108" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8668891191482544</v>
+        <v>0.8760305643081665</v>
       </c>
       <c r="F108" t="n">
-        <v>0.003749325172975659</v>
+        <v>0.006920611951500177</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4523,10 +4535,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.947293758392334</v>
+        <v>0.9411950707435608</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2365555167198181</v>
+        <v>0.2300711125135422</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4544,16 +4556,16 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D109" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9500114321708679</v>
+        <v>0.9491831064224243</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2508744895458221</v>
+        <v>0.2601138651371002</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9115869402885437</v>
+        <v>0.8678911924362183</v>
       </c>
       <c r="I109" t="n">
-        <v>0.03818437084555626</v>
+        <v>0.008775687776505947</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4582,16 +4594,16 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D110" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9631301760673523</v>
+        <v>0.9654224514961243</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4802725315093994</v>
+        <v>0.5564827919006348</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4599,10 +4611,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9377729296684265</v>
+        <v>0.9606651663780212</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1454820334911346</v>
+        <v>0.5296261310577393</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4620,16 +4632,16 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D111" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9076820611953735</v>
+        <v>0.9134055972099304</v>
       </c>
       <c r="F111" t="n">
-        <v>0.02706661447882652</v>
+        <v>0.04183515906333923</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4637,14 +4649,14 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.8239866495132446</v>
+        <v>0.9677441716194153</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0007464339141733944</v>
+        <v>0.6827679872512817</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4658,16 +4670,16 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D112" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9610897302627563</v>
+        <v>0.9639368653297424</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4366047382354736</v>
+        <v>0.5224425792694092</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4675,10 +4687,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.8629139065742493</v>
+        <v>0.8391189575195312</v>
       </c>
       <c r="I112" t="n">
-        <v>0.003833132795989513</v>
+        <v>0.002774578053504229</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4696,16 +4708,16 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D113" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9691609144210815</v>
+        <v>0.9663230776786804</v>
       </c>
       <c r="F113" t="n">
-        <v>0.6238660216331482</v>
+        <v>0.5776436924934387</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4713,14 +4725,14 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.8204823732376099</v>
+        <v>0.924294114112854</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0006493613473139703</v>
+        <v>0.1057693585753441</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4746,16 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D114" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9716291427612305</v>
+        <v>0.9711524844169617</v>
       </c>
       <c r="F114" t="n">
-        <v>0.6865819692611694</v>
+        <v>0.6954922676086426</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4751,14 +4763,14 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.9345932006835938</v>
+        <v>0.8803636431694031</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1235089749097824</v>
+        <v>0.01483521610498428</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4772,16 +4784,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D115" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9687235951423645</v>
+        <v>0.9670385718345642</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6128922700881958</v>
+        <v>0.5947021245956421</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4789,10 +4801,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.9479660987854004</v>
+        <v>0.9326633810997009</v>
       </c>
       <c r="I115" t="n">
-        <v>0.244704395532608</v>
+        <v>0.1556483656167984</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4810,27 +4822,27 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D116" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9224686622619629</v>
+        <v>0.9093477129936218</v>
       </c>
       <c r="F116" t="n">
-        <v>0.05833170562982559</v>
+        <v>0.03414016216993332</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9583364129066467</v>
+        <v>0.9445987343788147</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4059207737445831</v>
+        <v>0.2682634890079498</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4848,16 +4860,16 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D117" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9217528104782104</v>
+        <v>0.9294579029083252</v>
       </c>
       <c r="F117" t="n">
-        <v>0.05617456138134003</v>
+        <v>0.09480451792478561</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4865,14 +4877,14 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.9217270612716675</v>
+        <v>0.8692864179611206</v>
       </c>
       <c r="I117" t="n">
-        <v>0.06378266215324402</v>
+        <v>0.009299206547439098</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4886,16 +4898,16 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D118" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9611942768096924</v>
+        <v>0.957694947719574</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4387715756893158</v>
+        <v>0.3938861787319183</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4903,14 +4915,14 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.9322866201400757</v>
+        <v>0.9067291021347046</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1096691787242889</v>
+        <v>0.04734399169683456</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4936,16 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D119" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9026526808738708</v>
+        <v>0.8951899409294128</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02096525020897388</v>
+        <v>0.0170433409512043</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4941,10 +4953,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.9629589915275574</v>
+        <v>0.9673926830291748</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5006915926933289</v>
+        <v>0.6749210357666016</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4962,16 +4974,16 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D120" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8742761015892029</v>
+        <v>0.8743437528610229</v>
       </c>
       <c r="F120" t="n">
-        <v>0.005276943556964397</v>
+        <v>0.006406706292182207</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4979,14 +4991,14 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0.9032862782478333</v>
+        <v>0.9111917018890381</v>
       </c>
       <c r="I120" t="n">
-        <v>0.02528423070907593</v>
+        <v>0.05796924605965614</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -5000,16 +5012,16 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9733221530914307</v>
+        <v>0.9594173431396484</v>
       </c>
       <c r="F121" t="n">
-        <v>0.7297186255455017</v>
+        <v>0.4268283247947693</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5017,10 +5029,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0.9441854953765869</v>
+        <v>0.939554750919342</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2020676732063293</v>
+        <v>0.2135299444198608</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
